--- a/error_models/conv_models/nv_32x32_b1_dat-2097152_wt-524288_int32/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_32x32_b1_dat-2097152_wt-524288_int32/unique_complete_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:AT40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,136 @@
           <t>Skip4</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-single</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-multi</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-single</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-multi</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>single-single</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>single-multi</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-single</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-multi</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-single</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-multi</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-single</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-multi</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-single</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-multi</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-multi</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-single</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-multi</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-single</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-multi</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-single</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-multi</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-single</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-multi</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-multi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -552,13 +682,13 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9966527146442968</v>
+        <v>0.9974132567646752</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0033432902247024</v>
+        <v>0.0025834758262625</v>
       </c>
       <c r="I2" t="n">
-        <v>3.972458055551656e-06</v>
+        <v>3.244736116759505e-06</v>
       </c>
       <c r="J2" t="n">
         <v>0.7612622236950851</v>
@@ -579,7 +709,7 @@
         <v>0.05593993531146</v>
       </c>
       <c r="P2" t="n">
-        <v>8.614897294403157e-07</v>
+        <v>8.614897294403156e-07</v>
       </c>
       <c r="Q2" t="n">
         <v>3.1466538863894e-05</v>
@@ -592,6 +722,84 @@
       </c>
       <c r="T2" t="n">
         <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.2038009133162459</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.7961990866837541</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -616,13 +824,13 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9954883776225628</v>
+        <v>0.9958148360096596</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0045072645099239</v>
+        <v>0.0041814548137914</v>
       </c>
       <c r="I3" t="n">
-        <v>4.335194568153086e-06</v>
+        <v>3.686503603531399e-06</v>
       </c>
       <c r="J3" t="n">
         <v>0.3505939822748278</v>
@@ -656,6 +864,84 @@
       </c>
       <c r="T3" t="n">
         <v>0.0002651726519869</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.2038009052652441</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.7961990947347558</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -680,13 +966,13 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.999088524029718</v>
+        <v>0.9991230796147595</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0009070916986171</v>
+        <v>0.0008730518838199999</v>
       </c>
       <c r="I4" t="n">
-        <v>4.361598719674695e-06</v>
+        <v>3.845828475067415e-06</v>
       </c>
       <c r="J4" t="n">
         <v>0.0392292527983065</v>
@@ -720,6 +1006,84 @@
       </c>
       <c r="T4" t="n">
         <v>7.697355171965856e-06</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.9945491665180076</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.0054508334819924</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.2038010112177599</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.79619898878224</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -744,13 +1108,13 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9977427221938244</v>
+        <v>0.9977669251572192</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0022528960231151</v>
+        <v>0.0022291966270553</v>
       </c>
       <c r="I5" t="n">
-        <v>4.359110115072094e-06</v>
+        <v>3.855542780309319e-06</v>
       </c>
       <c r="J5" t="n">
         <v>0.0095052129046334</v>
@@ -771,7 +1135,7 @@
         <v>0.0778082825049899</v>
       </c>
       <c r="P5" t="n">
-        <v>6.553091506890597e-07</v>
+        <v>6.553091506890596e-07</v>
       </c>
       <c r="Q5" t="n">
         <v>0.0002986352078415</v>
@@ -784,6 +1148,84 @@
       </c>
       <c r="T5" t="n">
         <v>0.0014958123145379</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.9998733471689134</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.0001266528310865</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.2038010319562307</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.7961989680437692</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -808,19 +1250,19 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9980809658145768</v>
+        <v>0.9981486721371148</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0019145869821065</v>
+        <v>0.0018473866741279</v>
       </c>
       <c r="I6" t="n">
-        <v>4.424530371463517e-06</v>
+        <v>3.91851581185684e-06</v>
       </c>
       <c r="J6" t="n">
         <v>0.0530765662943976</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7234514980458893</v>
+        <v>0.7234514980458892</v>
       </c>
       <c r="L6" t="n">
         <v>0.07460743744003021</v>
@@ -848,6 +1290,84 @@
       </c>
       <c r="T6" t="n">
         <v>0.0034080053970989</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.9998729363141412</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.0001270636858586</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.2038009966477515</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.7961990033522486</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -872,16 +1392,16 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9982520925740695</v>
+        <v>0.9989517292545076</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0017437446446103</v>
+        <v>0.0010448118442373</v>
       </c>
       <c r="I7" t="n">
-        <v>4.140108375000823e-06</v>
+        <v>3.436228309701532e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6740380266985115</v>
+        <v>0.6740380266985114</v>
       </c>
       <c r="K7" t="n">
         <v>0.1239958736861939</v>
@@ -912,6 +1432,84 @@
       </c>
       <c r="T7" t="n">
         <v>3.344887326957225e-07</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.2038039800547395</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.7961960199452605</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -936,13 +1534,13 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9976940496171716</v>
+        <v>0.998101454589954</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0023016298160401</v>
+        <v>0.001894889973058</v>
       </c>
       <c r="I8" t="n">
-        <v>4.297893843130076e-06</v>
+        <v>3.632764042488798e-06</v>
       </c>
       <c r="J8" t="n">
         <v>0.216792231114725</v>
@@ -963,7 +1561,7 @@
         <v>0.0450472383830885</v>
       </c>
       <c r="P8" t="n">
-        <v>1.485260346029326e-06</v>
+        <v>1.485260346029327e-06</v>
       </c>
       <c r="Q8" t="n">
         <v>0.0200807301824059</v>
@@ -976,6 +1574,84 @@
       </c>
       <c r="T8" t="n">
         <v>0.0054892280030081</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.2038009578709798</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.7961990421290203</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1000,13 +1676,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9993046280419912</v>
+        <v>0.9996646110450946</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0006904991216743</v>
+        <v>0.0003311609857695</v>
       </c>
       <c r="I9" t="n">
-        <v>4.850163389273959e-06</v>
+        <v>4.205296190607377e-06</v>
       </c>
       <c r="J9" t="n">
         <v>0.0528696375014748</v>
@@ -1040,6 +1716,84 @@
       </c>
       <c r="T9" t="n">
         <v>2.106354550315016e-05</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1064,19 +1818,19 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9992881804868342</v>
+        <v>0.9993540413402801</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0007075655083308</v>
+        <v>0.0006421561345447</v>
       </c>
       <c r="I10" t="n">
-        <v>4.231331889775184e-06</v>
+        <v>3.779852229833139e-06</v>
       </c>
       <c r="J10" t="n">
         <v>0.0477114380023073</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8275835926312567</v>
+        <v>0.8275835926312568</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1104,6 +1858,84 @@
       </c>
       <c r="T10" t="n">
         <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1128,19 +1960,19 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.999648383677046</v>
+        <v>0.9997600980308066</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0003473389207008</v>
+        <v>0.0002361713817193</v>
       </c>
       <c r="I11" t="n">
-        <v>4.254729308082172e-06</v>
+        <v>3.707914528909111e-06</v>
       </c>
       <c r="J11" t="n">
         <v>0.0441283987318205</v>
       </c>
       <c r="K11" t="n">
-        <v>0.837508862866456</v>
+        <v>0.8375088628664562</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1168,6 +2000,84 @@
       </c>
       <c r="T11" t="n">
         <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1192,13 +2102,13 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9991496812293292</v>
+        <v>0.9994120660528412</v>
       </c>
       <c r="H12" t="n">
-        <v>0.000845767565223</v>
+        <v>0.0005839291888667</v>
       </c>
       <c r="I12" t="n">
-        <v>4.528532502400015e-06</v>
+        <v>3.982085346885803e-06</v>
       </c>
       <c r="J12" t="n">
         <v>0.1151893307962584</v>
@@ -1219,7 +2129,7 @@
         <v>2.516839520851854e-09</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6650096012359116</v>
+        <v>0.6650096012359114</v>
       </c>
       <c r="Q12" t="n">
         <v>0.1792269636897211</v>
@@ -1232,6 +2142,84 @@
       </c>
       <c r="T12" t="n">
         <v>0.0040051793788238</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1256,13 +2244,13 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.999669779965876</v>
+        <v>0.999847364981128</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0003255966047224</v>
+        <v>0.0001486795534656</v>
       </c>
       <c r="I13" t="n">
-        <v>4.600756456386059e-06</v>
+        <v>3.932792460868623e-06</v>
       </c>
       <c r="J13" t="n">
         <v>0.0002592573060123</v>
@@ -1283,7 +2271,7 @@
         <v>3.385596309775345e-09</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8823134868335082</v>
+        <v>0.8823134868335083</v>
       </c>
       <c r="Q13" t="n">
         <v>0.095391096208979</v>
@@ -1296,6 +2284,84 @@
       </c>
       <c r="T13" t="n">
         <v>0.0052961964072297</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1320,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.998758087455248</v>
+        <v>0.9990191825290284</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0012374129027381</v>
+        <v>0.0009768167733247</v>
       </c>
       <c r="I14" t="n">
-        <v>4.47696906853842e-06</v>
+        <v>3.978024701576444e-06</v>
       </c>
       <c r="J14" t="n">
         <v>0.1100865494453073</v>
@@ -1360,6 +2426,84 @@
       </c>
       <c r="T14" t="n">
         <v>0.0024001729764912</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1384,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9995954307050114</v>
+        <v>0.9998331645673724</v>
       </c>
       <c r="H15" t="n">
-        <v>0.000399864500121</v>
+        <v>0.0001628023938604</v>
       </c>
       <c r="I15" t="n">
-        <v>4.682121922404337e-06</v>
+        <v>4.010365822064907e-06</v>
       </c>
       <c r="J15" t="n">
         <v>0.0693653371157696</v>
@@ -1424,6 +2568,84 @@
       </c>
       <c r="T15" t="n">
         <v>5.631073936765933e-06</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1448,13 +2670,13 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.999756653465563</v>
+        <v>0.9999013004125882</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0002389760776454</v>
+        <v>9.50168800492674e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>4.347783846288511e-06</v>
+        <v>3.660034417162792e-06</v>
       </c>
       <c r="J16" t="n">
         <v>0.038248359656221</v>
@@ -1475,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9122530144024956</v>
+        <v>0.9122530144024958</v>
       </c>
       <c r="Q16" t="n">
         <v>0.0192321878149669</v>
@@ -1488,6 +2710,84 @@
       </c>
       <c r="T16" t="n">
         <v>2.110042137783438e-05</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1512,16 +2812,16 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9991841609107228</v>
+        <v>0.9993272659834108</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0008114129897811</v>
+        <v>0.0006687890016919</v>
       </c>
       <c r="I17" t="n">
-        <v>4.403426550929221e-06</v>
+        <v>3.922341951912891e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0418158982233364</v>
+        <v>0.0418158982233363</v>
       </c>
       <c r="K17" t="n">
         <v>0.0053589525646052</v>
@@ -1552,6 +2852,84 @@
       </c>
       <c r="T17" t="n">
         <v>0.0036249889374842</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1576,13 +2954,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.999744572974986</v>
+        <v>0.9998703373082642</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0002510610805901</v>
+        <v>0.0001259910487144</v>
       </c>
       <c r="I18" t="n">
-        <v>4.343271478945304e-06</v>
+        <v>3.648970075972439e-06</v>
       </c>
       <c r="J18" t="n">
         <v>0.0002116234540177</v>
@@ -1603,7 +2981,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8961059142711486</v>
+        <v>0.8961059142711485</v>
       </c>
       <c r="Q18" t="n">
         <v>0.06939061133876789</v>
@@ -1616,6 +2994,84 @@
       </c>
       <c r="T18" t="n">
         <v>0.0047758910297806</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1640,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9994972907696248</v>
+        <v>0.9995622318597294</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0004983193658692</v>
+        <v>0.0004338676696388</v>
       </c>
       <c r="I19" t="n">
-        <v>4.367191560906868e-06</v>
+        <v>3.87779768652228e-06</v>
       </c>
       <c r="J19" t="n">
         <v>0.0050891225110449</v>
@@ -1670,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.06347646572767331</v>
+        <v>0.0634764657276734</v>
       </c>
       <c r="R19" t="n">
         <v>0.0020476072455021</v>
@@ -1680,6 +3136,84 @@
       </c>
       <c r="T19" t="n">
         <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1704,13 +3238,13 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.999761503051868</v>
+        <v>0.9998353814638392</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0002343012197274</v>
+        <v>0.0001610191057382</v>
       </c>
       <c r="I20" t="n">
-        <v>4.173055459170084e-06</v>
+        <v>3.576757477289196e-06</v>
       </c>
       <c r="J20" t="n">
         <v>0.0061593719616884</v>
@@ -1744,6 +3278,84 @@
       </c>
       <c r="T20" t="n">
         <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1768,13 +3380,13 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9993152476048892</v>
+        <v>0.999365348169692</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0006804458914891</v>
+        <v>0.000630799201182</v>
       </c>
       <c r="I21" t="n">
-        <v>4.283830676163954e-06</v>
+        <v>3.829956180585842e-06</v>
       </c>
       <c r="J21" t="n">
         <v>0.0110329465463563</v>
@@ -1808,6 +3420,84 @@
       </c>
       <c r="T21" t="n">
         <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1832,19 +3522,19 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0978042531761784</v>
+        <v>0.6171309711702221</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9021911564956956</v>
+        <v>0.3828648946554547</v>
       </c>
       <c r="I22" t="n">
-        <v>4.567655180769894e-06</v>
+        <v>4.111501377929307e-06</v>
       </c>
       <c r="J22" t="n">
         <v>8.545693392188937e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.998210063276199</v>
+        <v>0.9982100632761992</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1872,6 +3562,84 @@
       </c>
       <c r="T22" t="n">
         <v>1.254148055670535e-07</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1896,13 +3664,13 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9882881062068508</v>
+        <v>0.98932983097316</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0117073792444507</v>
+        <v>0.0106660874097337</v>
       </c>
       <c r="I23" t="n">
-        <v>4.491875753419955e-06</v>
+        <v>4.058944161125738e-06</v>
       </c>
       <c r="J23" t="n">
         <v>0.4263035089470389</v>
@@ -1936,6 +3704,84 @@
       </c>
       <c r="T23" t="n">
         <v>0.0003899421757513</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1960,13 +3806,13 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.997856729554922</v>
+        <v>0.998155355468715</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0021387270410373</v>
+        <v>0.0018405645952676</v>
       </c>
       <c r="I24" t="n">
-        <v>4.520731095443076e-06</v>
+        <v>4.057263071910002e-06</v>
       </c>
       <c r="J24" t="n">
         <v>0.07630208360590469</v>
@@ -2000,6 +3846,84 @@
       </c>
       <c r="T24" t="n">
         <v>0.0008729193650584</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2024,13 +3948,13 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9985037567699691</v>
+        <v>0.998632288169192</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0014917794885477</v>
+        <v>0.0013636884199725</v>
       </c>
       <c r="I25" t="n">
-        <v>4.44106853790457e-06</v>
+        <v>4.000737890265209e-06</v>
       </c>
       <c r="J25" t="n">
         <v>0.0710449367523131</v>
@@ -2051,7 +3975,7 @@
         <v>1.987965642401544e-09</v>
       </c>
       <c r="P25" t="n">
-        <v>0.6918224349426897</v>
+        <v>0.6918224349426895</v>
       </c>
       <c r="Q25" t="n">
         <v>0.1902769747303188</v>
@@ -2064,6 +3988,84 @@
       </c>
       <c r="T25" t="n">
         <v>0.0033140837780086</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2088,13 +4090,13 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9989370966107552</v>
+        <v>0.998953021327333</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0010587060055499</v>
+        <v>0.0010432595152889</v>
       </c>
       <c r="I26" t="n">
-        <v>4.17471074970302e-06</v>
+        <v>3.696484432806286e-06</v>
       </c>
       <c r="J26" t="n">
         <v>0.0049382407894332</v>
@@ -2118,7 +4120,7 @@
         <v>0.7822243863292749</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.57975304021014e-07</v>
+        <v>7.579753040210139e-07</v>
       </c>
       <c r="R26" t="n">
         <v>0.0029801617288247</v>
@@ -2128,6 +4130,84 @@
       </c>
       <c r="T26" t="n">
         <v>0.00490655196702</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.9998757418652996</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.0001242581347004</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.2038010297312929</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0.7961989702687069</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2152,13 +4232,13 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9967331476262024</v>
+        <v>0.9971175667547442</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0032625677540241</v>
+        <v>0.0028788137148647</v>
       </c>
       <c r="I27" t="n">
-        <v>4.261946828310027e-06</v>
+        <v>3.596857445883828e-06</v>
       </c>
       <c r="J27" t="n">
         <v>0.1523094799054985</v>
@@ -2192,6 +4272,84 @@
       </c>
       <c r="T27" t="n">
         <v>0.0077291497304364</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.2038009443778177</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.7961990556221823</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2216,13 +4374,13 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9986880013713422</v>
+        <v>0.9987716994312223</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0013076869369478</v>
+        <v>0.0012245679706886</v>
       </c>
       <c r="I28" t="n">
-        <v>4.289018764848005e-06</v>
+        <v>3.709925143634385e-06</v>
       </c>
       <c r="J28" t="n">
         <v>0.0389732722427369</v>
@@ -2243,7 +4401,7 @@
         <v>0.0585238416226982</v>
       </c>
       <c r="P28" t="n">
-        <v>0.7229574072292049</v>
+        <v>0.722957407229205</v>
       </c>
       <c r="Q28" t="n">
         <v>0.0073166021984045</v>
@@ -2256,6 +4414,84 @@
       </c>
       <c r="T28" t="n">
         <v>2.88440254497695e-05</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2280,13 +4516,13 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9958207703320848</v>
+        <v>0.9959473594162328</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0041749342320651</v>
+        <v>0.0040489170118774</v>
       </c>
       <c r="I29" t="n">
-        <v>4.272762904806063e-06</v>
+        <v>3.700898944550056e-06</v>
       </c>
       <c r="J29" t="n">
         <v>0.0820992740644878</v>
@@ -2307,7 +4543,7 @@
         <v>0.0585231245713988</v>
       </c>
       <c r="P29" t="n">
-        <v>0.6849863825911863</v>
+        <v>0.6849863825911862</v>
       </c>
       <c r="Q29" t="n">
         <v>0.0024397525286537</v>
@@ -2320,6 +4556,84 @@
       </c>
       <c r="T29" t="n">
         <v>0.006706907788383</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.9998123997786936</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.0001876002213062</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2344,13 +4658,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0967996816170158</v>
+        <v>0.6165519523726893</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9031960507854516</v>
+        <v>0.383444248895705</v>
       </c>
       <c r="I30" t="n">
-        <v>4.244924586932361e-06</v>
+        <v>3.776058660437059e-06</v>
       </c>
       <c r="J30" t="n">
         <v>1.248779035454293e-06</v>
@@ -2384,6 +4698,84 @@
       </c>
       <c r="T30" t="n">
         <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2408,19 +4800,19 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9967982452439468</v>
+        <v>0.9974756409737152</v>
       </c>
       <c r="H31" t="n">
-        <v>0.003197350576154</v>
+        <v>0.0025204577824812</v>
       </c>
       <c r="I31" t="n">
-        <v>4.381506953865957e-06</v>
+        <v>3.878570858230718e-06</v>
       </c>
       <c r="J31" t="n">
         <v>6.399212069806372e-05</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8416372302339703</v>
+        <v>0.8416372302339702</v>
       </c>
       <c r="L31" t="n">
         <v>2.27373570349704e-08</v>
@@ -2429,7 +4821,7 @@
         <v>0.0151850387481755</v>
       </c>
       <c r="N31" t="n">
-        <v>2.223839207480244e-05</v>
+        <v>2.223839207480243e-05</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2438,7 +4830,7 @@
         <v>1.574854723290036e-06</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.1430116594858312</v>
+        <v>0.1430116594858311</v>
       </c>
       <c r="R31" t="n">
         <v>2.844242657979879e-05</v>
@@ -2448,6 +4840,84 @@
       </c>
       <c r="T31" t="n">
         <v>2.844094253247276e-05</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2472,13 +4942,13 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9932973794505244</v>
+        <v>0.9940912660076004</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0066981478741323</v>
+        <v>0.0059047107001614</v>
       </c>
       <c r="I32" t="n">
-        <v>4.45000239810085e-06</v>
+        <v>4.000619292855771e-06</v>
       </c>
       <c r="J32" t="n">
         <v>8.562864418378887e-05</v>
@@ -2493,16 +4963,16 @@
         <v>0.0354157287133928</v>
       </c>
       <c r="N32" t="n">
-        <v>2.335783081182657e-05</v>
+        <v>2.335783081182656e-05</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>8.996959215803738e-07</v>
+        <v>8.996959215803739e-07</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.190519450599542</v>
+        <v>0.1905194505995421</v>
       </c>
       <c r="R32" t="n">
         <v>6.728094872452501e-05</v>
@@ -2512,6 +4982,84 @@
       </c>
       <c r="T32" t="n">
         <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2536,13 +5084,13 @@
         <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>0.986205941867807</v>
+        <v>0.986381310799896</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0137898977488683</v>
+        <v>0.0136152472277024</v>
       </c>
       <c r="I33" t="n">
-        <v>4.137710379322805e-06</v>
+        <v>3.419299456283128e-06</v>
       </c>
       <c r="J33" t="n">
         <v>0.0380622661132343</v>
@@ -2576,6 +5124,84 @@
       </c>
       <c r="T33" t="n">
         <v>0.0050129091437979</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.999868410262474</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.0001315897375261</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2600,19 +5226,19 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9825765799486949</v>
+        <v>0.9829660791452264</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0174192299480387</v>
+        <v>0.0170304482879937</v>
       </c>
       <c r="I34" t="n">
-        <v>4.167430321080788e-06</v>
+        <v>3.449893834396064e-06</v>
       </c>
       <c r="J34" t="n">
         <v>2.967750525127589e-05</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7610405453478177</v>
+        <v>0.7610405453478176</v>
       </c>
       <c r="L34" t="n">
         <v>2.506957480321572e-06</v>
@@ -2640,6 +5266,84 @@
       </c>
       <c r="T34" t="n">
         <v>0.0051502840134594</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.0059458740130253</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0.9940541259869746</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2664,16 +5368,16 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9985095647360467</v>
+        <v>0.9989647763230385</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0014862167492274</v>
+        <v>0.00103171370492475</v>
       </c>
       <c r="I35" t="n">
-        <v>4.195841780492651e-06</v>
+        <v>3.487299091346235e-06</v>
       </c>
       <c r="J35" t="n">
-        <v>0.533702315489742</v>
+        <v>0.5337023154897419</v>
       </c>
       <c r="K35" t="n">
         <v>0.2635199896383065</v>
@@ -2704,6 +5408,84 @@
       </c>
       <c r="T35" t="n">
         <v>2.991839695415346e-07</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.2038017228223843</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.7961982771776157</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2728,13 +5510,13 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9883529145720581</v>
+        <v>0.9900479752425199</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0116430173961318</v>
+        <v>0.009948661569994601</v>
       </c>
       <c r="I36" t="n">
-        <v>4.045358864639181e-06</v>
+        <v>3.3405145402908e-06</v>
       </c>
       <c r="J36" t="n">
         <v>0.7075885013968326</v>
@@ -2768,6 +5550,84 @@
       </c>
       <c r="T36" t="n">
         <v>0.00132282917743525</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0.0029732297378099</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0.99702677026219</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2792,16 +5652,16 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9934212400513126</v>
+        <v>0.9939449734068435</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00657453181286895</v>
+        <v>0.0060514488494485</v>
       </c>
       <c r="I37" t="n">
-        <v>4.205462873275183e-06</v>
+        <v>3.555070762424855e-06</v>
       </c>
       <c r="J37" t="n">
-        <v>0.3616468522848238</v>
+        <v>0.3616468522848239</v>
       </c>
       <c r="K37" t="n">
         <v>0.406646137164412</v>
@@ -2832,6 +5692,84 @@
       </c>
       <c r="T37" t="n">
         <v>0.0038744043065197</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.339271035212695e-08</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0.9999999866072896</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2856,13 +5794,13 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9935251944736012</v>
+        <v>0.9936862075992964</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0064705114720359</v>
+        <v>0.006310066345401851</v>
       </c>
       <c r="I38" t="n">
-        <v>4.271381417467443e-06</v>
+        <v>3.703382356469711e-06</v>
       </c>
       <c r="J38" t="n">
         <v>0.05804473845647155</v>
@@ -2896,6 +5834,84 @@
       </c>
       <c r="T38" t="n">
         <v>0.0038843164694929</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.5999024473217347</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.4000975526782652</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2920,13 +5936,13 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9954002619730188</v>
+        <v>0.9955177749955617</v>
       </c>
       <c r="H39" t="n">
-        <v>0.004595408860334875</v>
+        <v>0.004478375230534025</v>
       </c>
       <c r="I39" t="n">
-        <v>4.30649370101703e-06</v>
+        <v>3.82710095892635e-06</v>
       </c>
       <c r="J39" t="n">
         <v>0.02559029415760142</v>
@@ -2960,6 +5976,84 @@
       </c>
       <c r="T39" t="n">
         <v>0.00965099644499535</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.5499043236055408</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.2000956763944591</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.1528507789797795</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0.5971492210202205</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2984,13 +6078,13 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.998496257900803</v>
+        <v>0.9985455030650142</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00149941608525565</v>
+        <v>0.0014506426082081</v>
       </c>
       <c r="I40" t="n">
-        <v>4.303340996120138e-06</v>
+        <v>3.831653832325865e-06</v>
       </c>
       <c r="J40" t="n">
         <v>0.0636941447388675</v>
@@ -3008,13 +6102,13 @@
         <v>0.03804288536231485</v>
       </c>
       <c r="O40" t="n">
-        <v>0.04596487431623555</v>
+        <v>0.0459648743162356</v>
       </c>
       <c r="P40" t="n">
         <v>0.3424926435166717</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.581287887640575e-05</v>
+        <v>1.581287887640576e-05</v>
       </c>
       <c r="R40" t="n">
         <v>0.00600805122592195</v>
@@ -3024,6 +6118,84 @@
       </c>
       <c r="T40" t="n">
         <v>0.00545965508254405</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.4998865128362712</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.0001134871637288</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0.1019005340403469</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0.3980994659596531</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/error_models/conv_models/nv_32x32_b1_dat-2097152_wt-524288_int32/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_32x32_b1_dat-2097152_wt-524288_int32/unique_complete_df.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unique_complete_layers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,309 +425,314 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT40"/>
+  <dimension ref="A1:AV40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Channels_in</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Channels_out</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Input_size</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Kernel_size</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Padding</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Masked</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>SDC</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Crash+Hang</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>FullChannels</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Rectangles</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>SingleChannelRandom</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ShatteredChannel</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>QuasiShatteredChannel</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MultiChannelBlock</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>BulletWake</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>SameRow</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>SingleBlock</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Skip4</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>full_channels-single</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>full_channels-multi</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-single</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-multi</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>single-single</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>single-multi</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-single</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-multi</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>single_block-single</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>single_block-multi</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-single</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-multi</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>skip_4-single</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>skip_4-multi</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-single</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-multi</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>same_row-single</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>same_row-multi</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-single</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-multi</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-single</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-multi</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>rectangles-single</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>rectangles-multi</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-single</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-multi</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>64</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>32</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.9974132567646752</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.0025834758262625</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>3.244736116759505e-06</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.7612622236950851</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.0426538504891633</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.08950694490682221</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0.0057519258966731</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.033565745533973</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.05593993531146</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>8.614897294403156e-07</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>3.1466538863894e-05</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>3.709768551165241e-05</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>6.183047469668914e-05</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
@@ -736,25 +741,25 @@
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -772,105 +777,111 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
         <v>0.2038009133162459</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AT2" t="n">
         <v>0.7961990866837541</v>
       </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>64</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>192</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>12</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.9958148360096596</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.0041814548137914</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>3.686503603531399e-06</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.3505939822748278</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.44485457563393</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.09545638908704571</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.0208560121001912</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.0237756493524349</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.0435863630826278</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>1.231552451030969e-06</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.0160990035611571</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>6.144632961073684e-05</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.0004876686500171</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.0002651726519869</v>
       </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1</v>
-      </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
@@ -878,141 +889,147 @@
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
         <v>0.2038009052652441</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AT3" t="n">
         <v>0.7961990947347558</v>
       </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv3</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
         <v>192</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>384</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.9991230796147595</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.0008730518838199999</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>3.845828475067415e-06</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.0392292527983065</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.745250286028706</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.06396159895918729</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.0203054216403974</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.06340250521798479</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.0634003184654006</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>9.169199068909588e-07</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.0004408080641026</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.0023266867444477</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.0016744311401961</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>7.697355171965856e-06</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
@@ -1020,141 +1037,147 @@
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
       </c>
       <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
         <v>0.9945491665180076</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>0.0054508334819924</v>
       </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
       <c r="AK4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
         <v>0.2038010112177599</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AT4" t="n">
         <v>0.79619898878224</v>
       </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv4</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
         <v>384</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>256</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.9977669251572192</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.0022291966270553</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>3.855542780309319e-06</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.0095052129046334</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.7648184779898001</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.0494009763887724</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.0259911253518607</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.0561983942530021</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.0778082825049899</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>6.553091506890596e-07</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>0.0002986352078415</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>0.0050886877583098</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.0007483329774483</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>0.0014958123145379</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
@@ -1162,141 +1185,147 @@
         <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
         <v>0.9998733471689134</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AJ5" t="n">
         <v>0.0001266528310865</v>
       </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1</v>
-      </c>
       <c r="AK5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
         <v>0.2038010319562307</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AT5" t="n">
         <v>0.7961989680437692</v>
       </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv5</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
         <v>256</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>256</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.9981486721371148</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.0018473866741279</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>3.91851581185684e-06</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.0530765662943976</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.7234514980458892</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.07460743744003021</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.0211181712578851</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.0581197109789376</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.0528334237762912</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>5.6751038033639e-07</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>0.0055327119349656</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>0.0076420795658207</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0.0002097305921445</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.0034080053970989</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
@@ -1304,141 +1333,147 @@
         <v>1</v>
       </c>
       <c r="Y6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
       <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
         <v>0.9998729363141412</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AJ6" t="n">
         <v>0.0001270636858586</v>
       </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
         <v>0.2038009966477515</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AT6" t="n">
         <v>0.7961990033522486</v>
       </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>32</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>32</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>0.9989517292545076</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.0010448118442373</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>3.436228309701532e-06</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.6740380266985114</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.1239958736861939</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.0475899713939799</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.019502406580663</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.0634022452505263</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.0554741232718805</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>1.749443587328966e-06</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.0159435330782158</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>8.618832733952472e-06</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>4.309460202960658e-05</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>3.344887326957225e-07</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
@@ -1446,25 +1481,25 @@
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1473,114 +1508,120 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
         <v>0.2038039800547395</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AT7" t="n">
         <v>0.7961960199452605</v>
       </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
         <v>32</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>64</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>16</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.998101454589954</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.001894889973058</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>3.632764042488798e-06</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.216792231114725</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.574528622265233</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.0500601192715404</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>0.0214111351962999</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.0600644603674154</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.0450472383830885</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>1.485260346029327e-06</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.0200807301824059</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>0.0009671408179765</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>0.0005522622958665</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>0.0054892280030081</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
@@ -1588,25 +1629,25 @@
         <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1615,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1624,105 +1665,111 @@
         <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
         <v>0.2038009578709798</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AT8" t="n">
         <v>0.7961990421290203</v>
       </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.1.conv.1</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
         <v>32</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>16</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>16</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.9996646110450946</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.0003311609857695</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>4.205296190607377e-06</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.0528696375014748</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.7706259904564492</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>0.0004908088988444</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>3.046428462443105e-06</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>1.422571827202186e-07</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>2.979891356262025e-06</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.1758180406502047</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>3.27319649456378e-05</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>0.0001355357326313</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>2.106354550315016e-05</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
@@ -1730,25 +1777,25 @@
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1766,25 +1813,25 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -1793,92 +1840,98 @@
         <v>0</v>
       </c>
       <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.10.conv.2</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
         <v>384</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>64</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>8</v>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.9993540413402801</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.0006421561345447</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>3.779852229833139e-06</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.0477114380023073</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.8275835926312568</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>0.0044092553237151</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>2.961646764472192e-06</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>2.921649871298056e-07</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.114180149635842</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>0.0061122879221818</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1908,25 +1961,25 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -1935,92 +1988,98 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.12.conv.0.0</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
         <v>96</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>576</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>8</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.9997600980308066</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.0002361713817193</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>3.707914528909111e-06</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.0441283987318205</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.8375088628664562</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>5.828053760774116e-05</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>0.0951246296179097</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>1.653009287328599e-07</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>0.0191452803737396</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>0.0040343598985922</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -2050,25 +2109,25 @@
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -2077,78 +2136,84 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.2.conv.2</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="D12" t="n">
         <v>96</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>24</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.9994120660528412</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.0005839291888667</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>3.982085346885803e-06</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.1151893307962584</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0.0163085448431658</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>1.906605956448074e-06</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>2.516839520851854e-09</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.6650096012359114</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.1792269636897211</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>9.032924920695827e-05</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.0201681190111711</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.0040051793788238</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
@@ -2156,61 +2221,61 @@
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -2219,78 +2284,84 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.0.0</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="D13" t="n">
         <v>24</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>144</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>8</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.999847364981128</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.0001486795534656</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>3.932792460868623e-06</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.0002592573060123</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>0.0001787658690042</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>2.143192033755267e-06</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>3.385596309775345e-09</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>0.8823134868335083</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.095391096208979</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>7.454227517066867e-05</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.0164844858495203</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>0.0052961964072297</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
@@ -2298,25 +2369,25 @@
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2334,25 +2405,25 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -2361,78 +2432,84 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.2</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="D14" t="n">
         <v>144</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>24</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>0.9990191825290284</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.0009768167733247</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>3.978024701576444e-06</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.1100865494453073</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>0.0172109703408957</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>1.536572882833404e-06</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>0.6594986742898488</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.1842760658030927</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>7.54828896827004e-05</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.0264505250088534</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>0.0024001729764912</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1</v>
-      </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
@@ -2440,61 +2517,61 @@
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -2503,78 +2580,84 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.4.conv.0.0</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="D15" t="n">
         <v>24</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E15" t="n">
         <v>144</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.9998331645673724</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.0001628023938604</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>4.010365822064907e-06</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.0693653371157696</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>0.0049289497828195</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>2.031681381898892e-06</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.7788123974722362</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.1271105418150624</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>8.795883740035682e-05</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.0196871295484476</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>5.631073936765933e-06</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1</v>
-      </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
@@ -2582,25 +2665,25 @@
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2618,25 +2701,25 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -2645,78 +2728,84 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.0.0</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="D16" t="n">
         <v>32</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>192</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>4</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.9999013004125882</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>9.50168800492674e-05</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>3.660034417162792e-06</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.038248359656221</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.0001055065304318</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>1.533817621306094e-06</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>0.0038794001615289</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>3.632171828095475e-06</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.9122530144024958</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.0192321878149669</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>9.537572918785414e-05</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.026159866621395</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>2.110042137783438e-05</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1</v>
-      </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
@@ -2724,25 +2813,25 @@
         <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2760,25 +2849,25 @@
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -2787,78 +2876,84 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.2</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="D17" t="n">
         <v>192</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>32</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>0.9993272659834108</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.0006687890016919</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>3.922341951912891e-06</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.0418158982233363</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.0053589525646052</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>1.826769242183674e-05</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.02950236888166</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>3.369568216217222e-06</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>6.197895980621811e-09</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.7364239750813636</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.176860754462874</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>0.0027618013200231</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>0.0036295943971741</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>0.0036249889374842</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1</v>
-      </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
@@ -2866,58 +2961,58 @@
         <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ17" t="n">
         <v>1</v>
@@ -2926,81 +3021,87 @@
         <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.6.conv.0.0</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="D18" t="n">
         <v>32</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>192</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>2</v>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.9998703373082642</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.0001259910487144</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>3.648970075972439e-06</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.0002116234540177</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>6.501932336483301e-05</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>3.271583693096996e-06</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.0049817801721566</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>3.600087861053808e-06</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.8961059142711485</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.06939061133876789</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>8.634387419307994e-05</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.0243759221920709</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>0.0047758910297806</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1</v>
-      </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
@@ -3008,25 +3109,25 @@
         <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -3044,25 +3145,25 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -3071,92 +3172,98 @@
         <v>0</v>
       </c>
       <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.7.conv.2</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="D19" t="n">
         <v>192</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>64</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>0.9995622318597294</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.0004338676696388</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>3.87779768652228e-06</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.0050891225110449</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.9264032029662844</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.0029807096014606</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>2.858065635520141e-06</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>1.120945332816456e-08</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.0634764657276734</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>0.0020476072455021</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3186,25 +3293,25 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -3213,92 +3320,98 @@
         <v>0</v>
       </c>
       <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.8.conv.0.0</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="D20" t="n">
         <v>64</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>384</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>2</v>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>0.9998353814638392</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.0001610191057382</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>3.576757477289196e-06</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.0061593719616884</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.948351265902224</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>0.0030247781157301</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>2.801436911766138e-06</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>2.458162794807056e-08</v>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>0.0423663810679048</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>9.53542609674344e-05</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -3328,25 +3441,25 @@
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -3355,92 +3468,98 @@
         <v>0</v>
       </c>
       <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.9.conv.2</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="D21" t="n">
         <v>384</v>
       </c>
-      <c r="C21" t="n">
+      <c r="E21" t="n">
         <v>64</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
       <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.999365348169692</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.000630799201182</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>3.829956180585842e-06</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.0110329465463563</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.913805312117876</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.0114585685528541</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>2.722990985887987e-06</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>1.275933034618143e-07</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>0.0571409684523283</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0.0065593310733505</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3470,25 +3589,25 @@
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -3497,78 +3616,84 @@
         <v>0</v>
       </c>
       <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>res50_cifar10_layer1.2.conv1</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="D22" t="n">
         <v>256</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
         <v>64</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>32</v>
       </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>0.6171309711702221</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.3828648946554547</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>4.111501377929307e-06</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>8.545693392188937e-05</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.9982100632761992</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>6.780390527919001e-06</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>2.098110544143802e-08</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
         <v>5.883770255912789e-09</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>0.0016971482023075</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>2.508296111341069e-07</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>1.254148055670535e-07</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
         <v>1.254148055670535e-07</v>
       </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1</v>
-      </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
@@ -3576,13 +3701,13 @@
         <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3621,16 +3746,16 @@
         <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR22" t="n">
         <v>0</v>
@@ -3639,78 +3764,84 @@
         <v>0</v>
       </c>
       <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>res50_cifar10_layer2.1.conv1</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="D23" t="n">
         <v>512</v>
       </c>
-      <c r="C23" t="n">
+      <c r="E23" t="n">
         <v>128</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>16</v>
       </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>0.98932983097316</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.0106660874097337</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>4.058944161125738e-06</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.4263035089470389</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.3493263253054154</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>0.0370896409915108</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>1.52182292451336e-06</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.24931983925566e-06</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.1868263141630781</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>2.720724604258608e-05</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>3.426735545364138e-05</v>
       </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
         <v>0.0003899421757513</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1</v>
-      </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
@@ -3718,25 +3849,25 @@
         <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3754,105 +3885,111 @@
         <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
         <v>0</v>
       </c>
       <c r="AT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>res50_cifar10_layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="D24" t="n">
         <v>256</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>1024</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>8</v>
       </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
       <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.998155355468715</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.0018405645952676</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>4.057263071910002e-06</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.07630208360590469</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.0357787437285491</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>1.17342323231898e-06</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
         <v>0.6848307252910572</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.1903319608279935</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>7.111885733377436e-05</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.0118112522279256</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>0.0008729193650584</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
@@ -3860,25 +3997,25 @@
         <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3896,25 +4033,25 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
@@ -3923,78 +4060,84 @@
         <v>0</v>
       </c>
       <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>res50_cifar10_layer4.1.conv3</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="D25" t="n">
         <v>512</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>2048</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>4</v>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
       <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>0.998632288169192</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.0013636884199725</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>4.000737890265209e-06</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.0710449367523131</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.0049405756877024</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>0.0003287373224661</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>0.0316473607057566</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>1.901347008485736e-06</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>1.987965642401544e-09</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>0.6918224349426895</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.1902769747303188</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>0.0040057621443081</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.0026172079285171</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.0033140837780086</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
@@ -4002,58 +4145,58 @@
         <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
         <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ25" t="n">
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ25" t="n">
         <v>1</v>
@@ -4062,81 +4205,87 @@
         <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.11</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="D26" t="n">
         <v>256</v>
       </c>
-      <c r="C26" t="n">
+      <c r="E26" t="n">
         <v>512</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>16</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
         <v>0.998953021327333</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.0010432595152889</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>3.696484432806286e-06</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.0049382407894332</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.0049194544482867</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.06794445222258511</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.0228169632013486</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.0211368922320247</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.08453238485403131</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>0.7822243863292749</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>7.579753040210139e-07</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>0.0029801617288247</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.0035997315789209</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>0.00490655196702</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1</v>
-      </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
@@ -4144,141 +4293,147 @@
         <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
       </c>
       <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
         <v>0.9998757418652996</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AJ26" t="n">
         <v>0.0001242581347004</v>
       </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
       <c r="AK26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
         <v>0.2038010297312929</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AT26" t="n">
         <v>0.7961989702687069</v>
       </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.3</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="D27" t="n">
         <v>64</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>128</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>4</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
         <v>0.9971175667547442</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.0028788137148647</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>3.596857445883828e-06</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.1523094799054985</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.6344656571288801</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.0745448502743412</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.0278286824874108</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.0462663058248</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.0411244286313961</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>1.451450058423888e-06</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>0.0130465236482856</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>0.0026071565504777</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>7.618000769586668e-05</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>0.0077291497304364</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
@@ -4286,25 +4441,25 @@
         <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4313,114 +4468,120 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
         <v>0.2038009443778177</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AT27" t="n">
         <v>0.7961990556221823</v>
       </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.6</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="D28" t="n">
         <v>128</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>256</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>2</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>3</v>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
         <v>0.9987716994312223</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.0012245679706886</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>3.709925143634385e-06</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.0389732722427369</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0.07315730557137171</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>0.0246606751634919</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.0438946506649101</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.0585238416226982</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.722957407229205</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>0.0073166021984045</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>7.787525556986399e-05</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0.0230941128259885</v>
       </c>
-      <c r="T28" t="n">
+      <c r="V28" t="n">
         <v>2.88440254497695e-05</v>
       </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
@@ -4428,25 +4589,25 @@
         <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4455,7 +4616,7 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4464,105 +4625,111 @@
         <v>1</v>
       </c>
       <c r="AK28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
         <v>0</v>
       </c>
       <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.8</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="D29" t="n">
         <v>256</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>256</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>2</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>3</v>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
         <v>0.9959473594162328</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.0040489170118774</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>3.700898944550056e-06</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.0820992740644878</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0.07559985564099531</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.0361147646007077</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.0438930401922385</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.0585231245713988</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.6849863825911862</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>0.0024397525286537</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>0.0020478330217219</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.002712147860727</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>0.006706907788383</v>
       </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
@@ -4570,132 +4737,138 @@
         <v>1</v>
       </c>
       <c r="Y29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
       </c>
       <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
         <v>0.9998123997786936</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AJ29" t="n">
         <v>0.0001876002213062</v>
       </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
       <c r="AK29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
         <v>0</v>
       </c>
       <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.0.conv1</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="D30" t="n">
         <v>256</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>128</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>32</v>
       </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>0.6165519523726893</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.383444248895705</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>3.776058660437059e-06</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>1.248779035454293e-06</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.9974815504247236</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>4.387911006748435e-09</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>8.741892079378945e-06</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>3.063112701284816e-07</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
         <v>1.072144088580857e-08</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.0025081148105944</v>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
@@ -4703,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -4715,7 +4888,7 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4757,96 +4930,102 @@
         <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
         <v>0</v>
       </c>
       <c r="AT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.3.conv3</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="D31" t="n">
         <v>128</v>
       </c>
-      <c r="C31" t="n">
+      <c r="E31" t="n">
         <v>512</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>16</v>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
       <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>0.9974756409737152</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.0025204577824812</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>3.878570858230718e-06</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>6.399212069806372e-05</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.8416372302339702</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>2.27373570349704e-08</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>0.0151850387481755</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>2.223839207480243e-05</v>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
         <v>1.574854723290036e-06</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>0.1430116594858311</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>2.844242657979879e-05</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>2.133738511232167e-05</v>
       </c>
-      <c r="T31" t="n">
+      <c r="V31" t="n">
         <v>2.844094253247276e-05</v>
       </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1</v>
-      </c>
       <c r="W31" t="n">
         <v>0</v>
       </c>
@@ -4857,7 +5036,7 @@
         <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4866,13 +5045,13 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4890,104 +5069,110 @@
         <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
         <v>0</v>
       </c>
       <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="D32" t="n">
         <v>256</v>
       </c>
-      <c r="C32" t="n">
+      <c r="E32" t="n">
         <v>1024</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>16</v>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>0.9940912660076004</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.0059047107001614</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>4.000619292855771e-06</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>8.562864418378887e-05</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.7738325133965794</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>6.596332150804662e-08</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>0.0354157287133928</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>2.335783081182656e-05</v>
       </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
         <v>8.996959215803739e-07</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.1905194505995421</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>6.728094872452501e-05</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>5.505153457713956e-05</v>
       </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -4999,7 +5184,7 @@
         <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -5008,13 +5193,13 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -5032,105 +5217,111 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
         <v>0</v>
       </c>
       <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.1.conv2</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="D33" t="n">
         <v>256</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>256</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>16</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>3</v>
       </c>
-      <c r="F33" t="n">
+      <c r="H33" t="n">
         <v>2</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>0.986381310799896</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.0136152472277024</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>3.419299456283128e-06</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.0380622661132343</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.7230016553517333</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>0.0003811058968205</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>0.0481081867161645</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.1852232907459524</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>1.29648023342744e-07</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>1.003988821845108e-06</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>0.0001626744119777</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>1.558510350956964e-05</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>3.117020701913927e-05</v>
       </c>
-      <c r="T33" t="n">
+      <c r="V33" t="n">
         <v>0.0050129091437979</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1</v>
-      </c>
       <c r="W33" t="n">
         <v>0</v>
       </c>
@@ -5141,7 +5332,7 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -5150,13 +5341,13 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -5165,114 +5356,120 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
         <v>0.999868410262474</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AT33" t="n">
         <v>0.0001315897375261</v>
       </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer4.0.conv2</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="D34" t="n">
         <v>512</v>
       </c>
-      <c r="C34" t="n">
+      <c r="E34" t="n">
         <v>512</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>16</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>3</v>
       </c>
-      <c r="F34" t="n">
+      <c r="H34" t="n">
         <v>2</v>
       </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
         <v>0.9829660791452264</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.0170304482879937</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>3.449893834396064e-06</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>2.967750525127589e-05</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.7610405453478176</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>2.506957480321572e-06</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>0.0482172436882105</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>0.1799490948168756</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>0.0051403905400113</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>1.140337998339825e-06</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>0.0001786863837199</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>0.0002607273158858</v>
       </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
         <v>2.968042034423772e-05</v>
       </c>
-      <c r="T34" t="n">
+      <c r="V34" t="n">
         <v>0.0051502840134594</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
       <c r="W34" t="n">
         <v>0</v>
       </c>
@@ -5283,7 +5480,7 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5292,129 +5489,135 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
       </c>
       <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
         <v>0.0059458740130253</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AJ34" t="n">
         <v>0.9940541259869746</v>
       </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1</v>
-      </c>
       <c r="AK34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
         <v>0</v>
       </c>
       <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>merge0</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="D35" t="n">
         <v>3</v>
       </c>
-      <c r="C35" t="n">
+      <c r="E35" t="n">
         <v>64</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>32</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>3</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
         <v>0.9989647763230385</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.00103171370492475</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>3.487299091346235e-06</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.5337023154897419</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.2635199896383065</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.07799800236906225</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>0.0115884865382291</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>0.08322482450681171</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.0148592815650488</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>1.094557683822083e-06</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>0.0150465522529462</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>5.925486135715964e-06</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>5.320573911887386e-05</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
         <v>2.991839695415346e-07</v>
       </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1</v>
-      </c>
       <c r="W35" t="n">
         <v>0</v>
       </c>
@@ -5422,25 +5625,25 @@
         <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -5449,114 +5652,120 @@
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
         <v>0.5</v>
       </c>
-      <c r="AK35" t="n">
+      <c r="AM35" t="n">
         <v>0.5</v>
       </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
       <c r="AN35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
         <v>0.2038017228223843</v>
       </c>
-      <c r="AR35" t="n">
+      <c r="AT35" t="n">
         <v>0.7961982771776157</v>
       </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>merge1</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="D36" t="n">
         <v>64</v>
       </c>
-      <c r="C36" t="n">
+      <c r="E36" t="n">
         <v>64</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>32</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>3</v>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
         <v>0.9900479752425199</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.009948661569994601</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>3.3405145402908e-06</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.7075885013968326</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.07529945372399795</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>0.1026384081525257</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>0.0287440596151665</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.0352918779480563</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>0.03459056828933635</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>9.952352774594702e-07</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>0.01235072192077835</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>0.001083420328537983</v>
       </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
         <v>2.353639652118961e-05</v>
       </c>
-      <c r="T36" t="n">
+      <c r="V36" t="n">
         <v>0.00132282917743525</v>
       </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1</v>
-      </c>
       <c r="W36" t="n">
         <v>0</v>
       </c>
@@ -5564,25 +5773,25 @@
         <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5591,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5600,105 +5809,111 @@
         <v>1</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
         <v>0.0029732297378099</v>
       </c>
-      <c r="AR36" t="n">
+      <c r="AT36" t="n">
         <v>0.99702677026219</v>
       </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>merge2</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="D37" t="n">
         <v>128</v>
       </c>
-      <c r="C37" t="n">
+      <c r="E37" t="n">
         <v>128</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>16</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>3</v>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.9939449734068435</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.0060514488494485</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>3.555070762424855e-06</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.3616468522848239</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.406646137164412</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>0.1024017160192684</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>0.04141996112776055</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>0.03867074306463765</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>0.03809039869984965</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>1.227656332492009e-06</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>0.007054401563086799</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>0.00016411751191495</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>3.001121830479883e-05</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
         <v>0.0038744043065197</v>
       </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1</v>
-      </c>
       <c r="W37" t="n">
         <v>0</v>
       </c>
@@ -5706,25 +5921,25 @@
         <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5733,114 +5948,120 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
         <v>1.339271035212695e-08</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AT37" t="n">
         <v>0.9999999866072896</v>
       </c>
-      <c r="AS37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="n">
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>merge3</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="D38" t="n">
         <v>256</v>
       </c>
-      <c r="C38" t="n">
+      <c r="E38" t="n">
         <v>256</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>8</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>3</v>
       </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
         <v>0.9936862075992964</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.006310066345401851</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>3.703382356469711e-06</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.05804473845647155</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0.0878935357352276</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>0.04174099249866215</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>0.05796142393849835</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0.0387419315620695</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>0.7040197329509653</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>0.003289336401633984</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>0.0006239875978668</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.0037999548755928</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>0.0038843164694929</v>
       </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1</v>
-      </c>
       <c r="W38" t="n">
         <v>0</v>
       </c>
@@ -5848,353 +6069,371 @@
         <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
       </c>
       <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
         <v>0.5999024473217347</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AJ38" t="n">
         <v>0.4000975526782652</v>
       </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
       <c r="AK38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
         <v>0.1</v>
       </c>
-      <c r="AR38" t="n">
+      <c r="AT38" t="n">
         <v>0.9</v>
       </c>
-      <c r="AS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="n">
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>merge4</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="D39" t="n">
         <v>512</v>
       </c>
-      <c r="C39" t="n">
+      <c r="E39" t="n">
         <v>512</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>4</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>3</v>
       </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
         <v>0.9955177749955617</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.004478375230534025</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>3.82710095892635e-06</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.02559029415760142</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.2217728389031417</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.02701236537380053</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>0.01837277967837825</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.06314460313369162</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.06373720845660832</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.5613021233634738</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>3.974583923555118e-05</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>0.007624278395896225</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.0003542324667399</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.00965099644499535</v>
       </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1</v>
-      </c>
       <c r="W39" t="n">
         <v>0</v>
       </c>
       <c r="X39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
         <v>0.75</v>
       </c>
-      <c r="Y39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
       </c>
       <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
         <v>0.75</v>
       </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
       <c r="AF39" t="n">
         <v>0</v>
       </c>
       <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
         <v>0.5499043236055408</v>
       </c>
-      <c r="AH39" t="n">
+      <c r="AJ39" t="n">
         <v>0.2000956763944591</v>
       </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
       <c r="AK39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
         <v>0.1528507789797795</v>
       </c>
-      <c r="AR39" t="n">
+      <c r="AT39" t="n">
         <v>0.5971492210202205</v>
       </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>merge5</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="D40" t="n">
         <v>512</v>
       </c>
-      <c r="C40" t="n">
+      <c r="E40" t="n">
         <v>512</v>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
         <v>8</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>3</v>
       </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
         <v>0.9985455030650142</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.0014506426082081</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>3.831653832325865e-06</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.0636941447388675</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.4743724928318815</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.0097787271701289</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>0.009349069556616251</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>0.03804288536231485</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>0.0459648743162356</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>0.3424926435166717</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>1.581287887640576e-05</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>0.00600805122592195</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>6.675939748505e-05</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>0.00545965508254405</v>
       </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1</v>
-      </c>
       <c r="W40" t="n">
         <v>0</v>
       </c>
       <c r="X40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
         <v>0.5</v>
       </c>
-      <c r="Y40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
       </c>
       <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
       <c r="AF40" t="n">
         <v>0</v>
       </c>
       <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
         <v>0.4998865128362712</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AJ40" t="n">
         <v>0.0001134871637288</v>
       </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
       <c r="AK40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
         <v>0.1019005340403469</v>
       </c>
-      <c r="AR40" t="n">
+      <c r="AT40" t="n">
         <v>0.3980994659596531</v>
       </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
         <v>1</v>
       </c>
     </row>
